--- a/ResourcesPH/productPrice.xlsx
+++ b/ResourcesPH/productPrice.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="41">
   <si>
     <t>Code*</t>
   </si>
@@ -130,6 +130,18 @@
   </si>
   <si>
     <t>2025-10-29</t>
+  </si>
+  <si>
+    <t>2025-10-31</t>
+  </si>
+  <si>
+    <t>2025-11-03</t>
+  </si>
+  <si>
+    <t>2025-11-04</t>
+  </si>
+  <si>
+    <t>2025-11-10</t>
   </si>
 </sst>
 </file>
@@ -545,19 +557,19 @@
         <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>5262.0</v>
+        <v>5004.0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>6921.0</v>
+        <v>2746.0</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>8134.0</v>
+        <v>9077.0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>4150.0</v>
+        <v>1949.0</v>
       </c>
       <c r="N2" s="1">
         <v>0</v>
